--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY137"/>
+  <dimension ref="A1:AZ137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -811,6 +816,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124656805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -950,6 +960,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124656864</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1089,6 +1104,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657764</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1196,6 +1216,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Äspåsarna</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132714165</t>
         </is>
       </c>
     </row>
@@ -1303,6 +1328,11 @@
           <t>Äspåsarna</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132714331</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1447,6 +1477,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125005619</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1591,6 +1626,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125005789</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1693,6 +1733,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856640</t>
         </is>
       </c>
     </row>
@@ -1830,6 +1875,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655577</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1962,6 +2012,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655629</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2102,6 +2157,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655765</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2242,6 +2302,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655814</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2377,6 +2442,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657935</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2512,6 +2582,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657975</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2647,6 +2722,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004453</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2787,6 +2867,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004899</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2919,6 +3004,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125008620</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3041,6 +3131,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125009149</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3146,6 +3241,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856325</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3251,6 +3351,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856385</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3356,6 +3461,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856166</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3461,6 +3571,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856419</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3578,6 +3693,11 @@
           <t>Äspåsarna</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132714274</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3715,6 +3835,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655420</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3856,6 +3981,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900982</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3997,6 +4127,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901044</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4139,6 +4274,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901143</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4266,6 +4406,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655344</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4385,6 +4530,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004354</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4526,6 +4676,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655379</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4657,6 +4812,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900809</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4780,6 +4940,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655510</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4904,6 +5069,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655582</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5028,6 +5198,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655729</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5152,6 +5327,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655741</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5276,6 +5456,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655786</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5400,6 +5585,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655848</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5524,6 +5714,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655897</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5648,6 +5843,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655907</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5772,6 +5972,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655922</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5896,6 +6101,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655934</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6020,6 +6230,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655938</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6144,6 +6359,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655969</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6268,6 +6488,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124656023</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6392,6 +6617,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124656127</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6516,6 +6746,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657169</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6640,6 +6875,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657947</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6764,6 +7004,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657993</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6888,6 +7133,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901093</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6998,6 +7248,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901155</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7117,6 +7372,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004421</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7241,6 +7501,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004789</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7365,6 +7630,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004796</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7489,6 +7759,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004839</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7613,6 +7888,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004954</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7737,6 +8017,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004975</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7861,6 +8146,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125005041</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7985,6 +8275,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125005804</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8105,6 +8400,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125009113</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8229,6 +8529,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125009288</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8353,6 +8658,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125009368</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8477,6 +8787,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125009419</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8601,6 +8916,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125009984</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8725,6 +9045,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125010069</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8849,6 +9174,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125010225</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8973,6 +9303,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125010263</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9097,6 +9432,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125010323</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9221,6 +9561,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125010374</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9326,6 +9671,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856123</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9431,6 +9781,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856144</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9536,6 +9891,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856154</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9641,6 +10001,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856181</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9746,6 +10111,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856189</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9851,6 +10221,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856476</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9961,6 +10336,11 @@
           <t>Äspåsarna</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132714201</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10075,6 +10455,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133830876</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10181,6 +10566,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133955367</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10286,6 +10676,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856456</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10391,6 +10786,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856502</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10497,6 +10897,11 @@
           <t>Äspåsarna</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132714303</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10603,6 +11008,11 @@
           <t>Äspåsarna</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132714333</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10700,6 +11110,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843645</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10797,6 +11212,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843646</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10894,6 +11314,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843647</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10991,6 +11416,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843648</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11088,6 +11518,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843649</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11185,6 +11620,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843651</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11282,6 +11722,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843654</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11379,6 +11824,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843655</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11476,6 +11926,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843656</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11573,6 +12028,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843658</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11670,6 +12130,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843659</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11767,6 +12232,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843660</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11864,6 +12334,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843661</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11961,6 +12436,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843662</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12058,6 +12538,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843663</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12155,6 +12640,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843664</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12252,6 +12742,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843665</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12349,6 +12844,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843666</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12446,6 +12946,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843667</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12543,6 +13048,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843668</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12640,6 +13150,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843670</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12737,6 +13252,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843672</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12834,6 +13354,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843675</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12931,6 +13456,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843676</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13028,6 +13558,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843677</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13125,6 +13660,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843678</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13222,6 +13762,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843679</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13319,6 +13864,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843680</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13416,6 +13966,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843681</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13513,6 +14068,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843682</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13610,6 +14170,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843684</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13707,6 +14272,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133843685</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13835,6 +14405,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655533</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13959,6 +14534,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004722</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14074,6 +14654,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655486</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14190,6 +14775,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655620</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14306,6 +14896,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655745</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14422,6 +15017,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655803</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14538,6 +15138,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655880</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14654,6 +15259,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124656637</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14760,6 +15370,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901164</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14872,6 +15487,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004359</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14974,6 +15594,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004379</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15076,6 +15701,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004686</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15182,6 +15812,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004697</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15298,6 +15933,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004719</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15414,6 +16054,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004797</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15530,6 +16175,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004813</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15646,6 +16296,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004848</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15762,6 +16417,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125010183</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15867,6 +16527,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125856477</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15991,6 +16656,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004808</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16115,6 +16785,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004990</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16239,6 +16914,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125005037</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16368,8 +17048,151 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ137"/>
+  <dimension ref="A1:AZ138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14542,41 +14542,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124655486</v>
+        <v>136127173</v>
       </c>
       <c r="B117" t="n">
-        <v>101326</v>
+        <v>102420</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -14585,13 +14589,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>502845</v>
+        <v>502947</v>
       </c>
       <c r="R117" t="n">
-        <v>6547946</v>
+        <v>6547955</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14615,12 +14619,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14629,40 +14633,31 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>kalkblandskog</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124655486</t>
+          <t>https://artportalen.se/Sighting/136127173</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124655620</v>
+        <v>124655486</v>
       </c>
       <c r="B118" t="n">
         <v>101326</v>
@@ -14705,10 +14700,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>502809</v>
+        <v>502845</v>
       </c>
       <c r="R118" t="n">
-        <v>6547888</v>
+        <v>6547946</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14749,7 +14744,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -14777,13 +14771,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124655620</t>
+          <t>https://artportalen.se/Sighting/124655486</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124655745</v>
+        <v>124655620</v>
       </c>
       <c r="B119" t="n">
         <v>101326</v>
@@ -14826,10 +14820,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>502813</v>
+        <v>502809</v>
       </c>
       <c r="R119" t="n">
-        <v>6547881</v>
+        <v>6547888</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14898,13 +14892,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124655745</t>
+          <t>https://artportalen.se/Sighting/124655620</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124655803</v>
+        <v>124655745</v>
       </c>
       <c r="B120" t="n">
         <v>101326</v>
@@ -14936,7 +14930,7 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -14947,10 +14941,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>502821</v>
+        <v>502813</v>
       </c>
       <c r="R120" t="n">
-        <v>6547874</v>
+        <v>6547881</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15019,13 +15013,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124655803</t>
+          <t>https://artportalen.se/Sighting/124655745</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124655880</v>
+        <v>124655803</v>
       </c>
       <c r="B121" t="n">
         <v>101326</v>
@@ -15057,7 +15051,7 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -15068,10 +15062,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>502785</v>
+        <v>502821</v>
       </c>
       <c r="R121" t="n">
-        <v>6547829</v>
+        <v>6547874</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15140,13 +15134,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124655880</t>
+          <t>https://artportalen.se/Sighting/124655803</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124656637</v>
+        <v>124655880</v>
       </c>
       <c r="B122" t="n">
         <v>101326</v>
@@ -15189,10 +15183,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>502749</v>
+        <v>502785</v>
       </c>
       <c r="R122" t="n">
-        <v>6547598</v>
+        <v>6547829</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15204,7 +15198,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Kumla</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -15261,13 +15255,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124656637</t>
+          <t>https://artportalen.se/Sighting/124655880</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124901164</v>
+        <v>124656637</v>
       </c>
       <c r="B123" t="n">
         <v>101326</v>
@@ -15310,10 +15304,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>502975</v>
+        <v>502749</v>
       </c>
       <c r="R123" t="n">
-        <v>6547955</v>
+        <v>6547598</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15325,7 +15319,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>Kumla</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -15340,12 +15334,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15358,6 +15352,16 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>kalkblandskog</t>
+        </is>
+      </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
@@ -15372,13 +15376,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124901164</t>
+          <t>https://artportalen.se/Sighting/124656637</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125004359</v>
+        <v>124901164</v>
       </c>
       <c r="B124" t="n">
         <v>101326</v>
@@ -15408,7 +15412,11 @@
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -15417,10 +15425,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503112</v>
+        <v>502975</v>
       </c>
       <c r="R124" t="n">
-        <v>6548043</v>
+        <v>6547955</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15450,19 +15458,9 @@
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>07:39</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>07:39</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15489,13 +15487,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004359</t>
+          <t>https://artportalen.se/Sighting/124901164</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125004379</v>
+        <v>125004359</v>
       </c>
       <c r="B125" t="n">
         <v>101326</v>
@@ -15534,10 +15532,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503075</v>
+        <v>503112</v>
       </c>
       <c r="R125" t="n">
-        <v>6548039</v>
+        <v>6548043</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15567,9 +15565,19 @@
           <t>2025-05-09</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15596,13 +15604,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004379</t>
+          <t>https://artportalen.se/Sighting/125004359</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125004686</v>
+        <v>125004379</v>
       </c>
       <c r="B126" t="n">
         <v>101326</v>
@@ -15641,10 +15649,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503014</v>
+        <v>503075</v>
       </c>
       <c r="R126" t="n">
-        <v>6548006</v>
+        <v>6548039</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15703,13 +15711,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004686</t>
+          <t>https://artportalen.se/Sighting/125004379</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125004697</v>
+        <v>125004686</v>
       </c>
       <c r="B127" t="n">
         <v>101326</v>
@@ -15739,11 +15747,7 @@
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -15752,10 +15756,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>502998</v>
+        <v>503014</v>
       </c>
       <c r="R127" t="n">
-        <v>6547981</v>
+        <v>6548006</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15814,13 +15818,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004697</t>
+          <t>https://artportalen.se/Sighting/125004686</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125004719</v>
+        <v>125004697</v>
       </c>
       <c r="B128" t="n">
         <v>101326</v>
@@ -15863,10 +15867,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>502988</v>
+        <v>502998</v>
       </c>
       <c r="R128" t="n">
-        <v>6547961</v>
+        <v>6547981</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15911,16 +15915,6 @@
       <c r="AG128" t="b">
         <v>0</v>
       </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>blandskog på kalk</t>
-        </is>
-      </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
@@ -15935,13 +15929,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004719</t>
+          <t>https://artportalen.se/Sighting/125004697</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125004797</v>
+        <v>125004719</v>
       </c>
       <c r="B129" t="n">
         <v>101326</v>
@@ -15984,10 +15978,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>502946</v>
+        <v>502988</v>
       </c>
       <c r="R129" t="n">
-        <v>6547953</v>
+        <v>6547961</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16056,13 +16050,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004797</t>
+          <t>https://artportalen.se/Sighting/125004719</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125004813</v>
+        <v>125004797</v>
       </c>
       <c r="B130" t="n">
         <v>101326</v>
@@ -16105,10 +16099,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>502975</v>
+        <v>502946</v>
       </c>
       <c r="R130" t="n">
-        <v>6547922</v>
+        <v>6547953</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16177,13 +16171,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004813</t>
+          <t>https://artportalen.se/Sighting/125004797</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125004848</v>
+        <v>125004813</v>
       </c>
       <c r="B131" t="n">
         <v>101326</v>
@@ -16226,10 +16220,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>502927</v>
+        <v>502975</v>
       </c>
       <c r="R131" t="n">
-        <v>6547877</v>
+        <v>6547922</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16298,13 +16292,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004848</t>
+          <t>https://artportalen.se/Sighting/125004813</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125010183</v>
+        <v>125004848</v>
       </c>
       <c r="B132" t="n">
         <v>101326</v>
@@ -16347,10 +16341,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>502969</v>
+        <v>502927</v>
       </c>
       <c r="R132" t="n">
-        <v>6547947</v>
+        <v>6547877</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16402,7 +16396,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Blandskog på kalk</t>
+          <t>blandskog på kalk</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -16419,13 +16413,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125010183</t>
+          <t>https://artportalen.se/Sighting/125004848</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125856477</v>
+        <v>125010183</v>
       </c>
       <c r="B133" t="n">
         <v>101326</v>
@@ -16455,7 +16449,11 @@
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -16464,10 +16462,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503073</v>
+        <v>502969</v>
       </c>
       <c r="R133" t="n">
-        <v>6547987</v>
+        <v>6547947</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16494,12 +16492,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16508,37 +16506,44 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>Blandskog på kalk</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Rolf Wedding, Jessica Bösel</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125856477</t>
+          <t>https://artportalen.se/Sighting/125010183</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125004808</v>
+        <v>125856477</v>
       </c>
       <c r="B134" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16546,38 +16551,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -16586,10 +16579,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>502975</v>
+        <v>503073</v>
       </c>
       <c r="R134" t="n">
-        <v>6547922</v>
+        <v>6547987</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16616,12 +16609,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16630,41 +16623,34 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>blandskog på kalk</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
+          <t>Rolf Wedding, Jessica Bösel</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004808</t>
+          <t>https://artportalen.se/Sighting/125856477</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125004990</v>
+        <v>125004808</v>
       </c>
       <c r="B135" t="n">
         <v>101228</v>
@@ -16715,10 +16701,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>502869</v>
+        <v>502975</v>
       </c>
       <c r="R135" t="n">
-        <v>6547769</v>
+        <v>6547922</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16787,13 +16773,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125004990</t>
+          <t>https://artportalen.se/Sighting/125004808</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125005037</v>
+        <v>125004990</v>
       </c>
       <c r="B136" t="n">
         <v>101228</v>
@@ -16833,7 +16819,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -16844,10 +16830,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>502970</v>
+        <v>502869</v>
       </c>
       <c r="R136" t="n">
-        <v>6547797</v>
+        <v>6547769</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16916,38 +16902,38 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125005037</t>
+          <t>https://artportalen.se/Sighting/125004990</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>124657967</v>
+        <v>125005037</v>
       </c>
       <c r="B137" t="n">
-        <v>103403</v>
+        <v>101228</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>223246</v>
+        <v>222771</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -16962,7 +16948,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -16973,10 +16959,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503152</v>
+        <v>502970</v>
       </c>
       <c r="R137" t="n">
-        <v>6547902</v>
+        <v>6547797</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17003,17 +16989,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>telning</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17033,7 +17014,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>kalkblandskog</t>
+          <t>blandskog på kalk</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -17049,6 +17030,140 @@
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125005037</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>124657967</v>
+      </c>
+      <c r="B138" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Äspåsarna, Nrk</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>503152</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6547902</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Kumla</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Hardemo</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>telning</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>kalkblandskog</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124657967</t>
         </is>
@@ -17192,6 +17307,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -14545,7 +14545,7 @@
         <v>136127173</v>
       </c>
       <c r="B117" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -14545,7 +14545,7 @@
         <v>136127173</v>
       </c>
       <c r="B117" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -14545,7 +14545,7 @@
         <v>136127173</v>
       </c>
       <c r="B117" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/S 421-2021 artfynd.xlsx
+++ b/artfynd/S 421-2021 artfynd.xlsx
@@ -14545,7 +14545,7 @@
         <v>136127173</v>
       </c>
       <c r="B117" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
